--- a/information_request_forms/006_online_school_setup_form--information_request_forms.xlsx
+++ b/information_request_forms/006_online_school_setup_form--information_request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1125,8 +1125,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'public',_'label':_'public'}</t>
+          <t>public</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Public', 'label': 'Public'}</t>
+          <t>Public</t>
         </is>
       </c>
     </row>
@@ -1171,12 +1171,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'private',_'label':_'private'}</t>
+          <t>private</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Private', 'label': 'Private'}</t>
+          <t>Private</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'both',_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Both', 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1222,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'primary',_'label':_'primary'}</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Primary', 'label': 'Primary'}</t>
+          <t>Primary</t>
         </is>
       </c>
     </row>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'secondary',_'label':_'secondary'}</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Secondary', 'label': 'Secondary'}</t>
+          <t>Secondary</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'tertiary',_'label':_'tertiary'}</t>
+          <t>tertiary</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Tertiary', 'label': 'Tertiary'}</t>
+          <t>Tertiary</t>
         </is>
       </c>
     </row>
@@ -1273,12 +1273,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'active',_'label':_'active'}</t>
+          <t>active</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Active', 'label': 'Active'}</t>
+          <t>Active</t>
         </is>
       </c>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'inactive',_'label':_'inactive'}</t>
+          <t>inactive</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Inactive', 'label': 'Inactive'}</t>
+          <t>Inactive</t>
         </is>
       </c>
     </row>
